--- a/technology2.xlsx
+++ b/technology2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26CF59A4-E897-4DE2-B7D9-C011FB57FBB9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E12A08B8-7C7E-43A0-9EEB-16DDD5C9742C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930" activeTab="6" xr2:uid="{D746D7D5-B0A8-4858-AD5A-93AA09E65399}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930" activeTab="3" xr2:uid="{D746D7D5-B0A8-4858-AD5A-93AA09E65399}"/>
   </bookViews>
   <sheets>
     <sheet name="id_tech" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="sub_imp" sheetId="6" r:id="rId6"/>
     <sheet name="trans_cop_imp" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -716,17 +716,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="E15">
-        <f>(300+1000+700)*(30+40+25)*0.2</f>
-        <v>38000</v>
-      </c>
-    </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="E16" s="1">
-        <f>2460000+E15</f>
-        <v>2498000</v>
-      </c>
+      <c r="E16" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/technology2.xlsx
+++ b/technology2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E12A08B8-7C7E-43A0-9EEB-16DDD5C9742C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96B4D9B1-125D-4E07-A80F-28D2A5E1D1AF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930" activeTab="3" xr2:uid="{D746D7D5-B0A8-4858-AD5A-93AA09E65399}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930" activeTab="2" xr2:uid="{D746D7D5-B0A8-4858-AD5A-93AA09E65399}"/>
   </bookViews>
   <sheets>
     <sheet name="id_tech" sheetId="2" r:id="rId1"/>
